--- a/src/main/resources/espacios/mathematical/0 - Mathematical Symbols.xlsx
+++ b/src/main/resources/espacios/mathematical/0 - Mathematical Symbols.xlsx
@@ -429,11 +429,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -460,9 +460,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3762360</xdr:colOff>
+      <xdr:colOff>3762000</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>875880</xdr:rowOff>
+      <xdr:rowOff>875520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -476,7 +476,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="0"/>
-          <a:ext cx="3762360" cy="875880"/>
+          <a:ext cx="3762000" cy="875520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -498,9 +498,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4543560</xdr:colOff>
+      <xdr:colOff>4543200</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>961560</xdr:rowOff>
+      <xdr:rowOff>961200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -514,7 +514,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="1080000"/>
-          <a:ext cx="4543560" cy="961560"/>
+          <a:ext cx="4543200" cy="961200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -536,9 +536,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4962600</xdr:colOff>
+      <xdr:colOff>4962240</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>1342800</xdr:rowOff>
+      <xdr:rowOff>1342440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -552,7 +552,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="2217600"/>
-          <a:ext cx="4962600" cy="1342800"/>
+          <a:ext cx="4962240" cy="1342440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -574,9 +574,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4819680</xdr:colOff>
+      <xdr:colOff>4819320</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>1285560</xdr:rowOff>
+      <xdr:rowOff>1285200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -590,7 +590,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="3809520"/>
-          <a:ext cx="4819680" cy="1285560"/>
+          <a:ext cx="4819320" cy="1285200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -612,9 +612,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4962600</xdr:colOff>
+      <xdr:colOff>4962240</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1714320</xdr:rowOff>
+      <xdr:rowOff>1713960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -628,7 +628,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="5325840"/>
-          <a:ext cx="4962600" cy="1714320"/>
+          <a:ext cx="4962240" cy="1713960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -650,9 +650,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4886640</xdr:colOff>
+      <xdr:colOff>4886280</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1104480</xdr:rowOff>
+      <xdr:rowOff>1104120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -666,7 +666,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="7277760"/>
-          <a:ext cx="4886640" cy="1104480"/>
+          <a:ext cx="4886280" cy="1104120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -688,9 +688,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4791240</xdr:colOff>
+      <xdr:colOff>4790880</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>1056960</xdr:rowOff>
+      <xdr:rowOff>1056600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -704,7 +704,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="8661240"/>
-          <a:ext cx="4791240" cy="1056960"/>
+          <a:ext cx="4790880" cy="1056600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -726,9 +726,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4791240</xdr:colOff>
+      <xdr:colOff>4790880</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>971280</xdr:rowOff>
+      <xdr:rowOff>970920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -742,7 +742,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="9855360"/>
-          <a:ext cx="4791240" cy="971280"/>
+          <a:ext cx="4790880" cy="970920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -764,9 +764,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5486760</xdr:colOff>
+      <xdr:colOff>5486400</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>1695240</xdr:rowOff>
+      <xdr:rowOff>1694880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -780,7 +780,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="11087280"/>
-          <a:ext cx="5486760" cy="1695240"/>
+          <a:ext cx="5486400" cy="1694880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -802,9 +802,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4962600</xdr:colOff>
+      <xdr:colOff>4962240</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>999720</xdr:rowOff>
+      <xdr:rowOff>999360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -818,7 +818,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="12925440"/>
-          <a:ext cx="4962600" cy="999720"/>
+          <a:ext cx="4962240" cy="999360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -840,9 +840,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5648400</xdr:colOff>
+      <xdr:colOff>5648040</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>1428480</xdr:rowOff>
+      <xdr:rowOff>1428120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -856,7 +856,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="14194800"/>
-          <a:ext cx="5648400" cy="1428480"/>
+          <a:ext cx="5648040" cy="1428120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -878,9 +878,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4552920</xdr:colOff>
+      <xdr:colOff>4552560</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>1171080</xdr:rowOff>
+      <xdr:rowOff>1170720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -894,7 +894,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="15786720"/>
-          <a:ext cx="4552920" cy="1171080"/>
+          <a:ext cx="4552560" cy="1170720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -916,9 +916,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5419800</xdr:colOff>
+      <xdr:colOff>5419440</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>1533240</xdr:rowOff>
+      <xdr:rowOff>1532880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -932,7 +932,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="17264880"/>
-          <a:ext cx="5419800" cy="1533240"/>
+          <a:ext cx="5419440" cy="1532880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -954,9 +954,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5391360</xdr:colOff>
+      <xdr:colOff>5391000</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>1618920</xdr:rowOff>
+      <xdr:rowOff>1618560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -970,7 +970,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="19046160"/>
-          <a:ext cx="5391360" cy="1618920"/>
+          <a:ext cx="5391000" cy="1618560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -992,9 +992,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5715360</xdr:colOff>
+      <xdr:colOff>5715000</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>933120</xdr:rowOff>
+      <xdr:rowOff>932760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1008,7 +1008,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="20998080"/>
-          <a:ext cx="5715360" cy="933120"/>
+          <a:ext cx="5715000" cy="932760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1030,9 +1030,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4429080</xdr:colOff>
+      <xdr:colOff>4428720</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>990360</xdr:rowOff>
+      <xdr:rowOff>990000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1046,7 +1046,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="22116240"/>
-          <a:ext cx="4429080" cy="990360"/>
+          <a:ext cx="4428720" cy="990000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1068,9 +1068,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3933720</xdr:colOff>
+      <xdr:colOff>3933360</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1523520</xdr:rowOff>
+      <xdr:rowOff>1523160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1084,7 +1084,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="23385960"/>
-          <a:ext cx="3933720" cy="1523520"/>
+          <a:ext cx="3933360" cy="1523160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1106,9 +1106,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4562640</xdr:colOff>
+      <xdr:colOff>4562280</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>1380600</xdr:rowOff>
+      <xdr:rowOff>1380240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1122,7 +1122,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="25185960"/>
-          <a:ext cx="4562640" cy="1380600"/>
+          <a:ext cx="4562280" cy="1380240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1144,9 +1144,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5886720</xdr:colOff>
+      <xdr:colOff>5886360</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>1552320</xdr:rowOff>
+      <xdr:rowOff>1551960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1160,7 +1160,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="26816040"/>
-          <a:ext cx="5886720" cy="1552320"/>
+          <a:ext cx="5886360" cy="1551960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1182,9 +1182,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3762360</xdr:colOff>
+      <xdr:colOff>3762000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>1380600</xdr:rowOff>
+      <xdr:rowOff>1380240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1198,7 +1198,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="28597320"/>
-          <a:ext cx="3762360" cy="1380600"/>
+          <a:ext cx="3762000" cy="1380240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1220,9 +1220,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4448160</xdr:colOff>
+      <xdr:colOff>4447800</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1218960</xdr:rowOff>
+      <xdr:rowOff>1218600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1236,7 +1236,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="30246480"/>
-          <a:ext cx="4448160" cy="1218960"/>
+          <a:ext cx="4447800" cy="1218600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1258,9 +1258,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3390840</xdr:colOff>
+      <xdr:colOff>3390480</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>923400</xdr:rowOff>
+      <xdr:rowOff>923040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1274,7 +1274,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="31781160"/>
-          <a:ext cx="3390840" cy="923400"/>
+          <a:ext cx="3390480" cy="923040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1296,9 +1296,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3324240</xdr:colOff>
+      <xdr:colOff>3323880</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>1066320</xdr:rowOff>
+      <xdr:rowOff>1065960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1312,7 +1312,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="32936760"/>
-          <a:ext cx="3324240" cy="1066320"/>
+          <a:ext cx="3323880" cy="1065960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1334,9 +1334,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3981600</xdr:colOff>
+      <xdr:colOff>3981240</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>1142640</xdr:rowOff>
+      <xdr:rowOff>1142280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1350,7 +1350,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="34263360"/>
-          <a:ext cx="3981600" cy="1142640"/>
+          <a:ext cx="3981240" cy="1142280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1372,9 +1372,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3828960</xdr:colOff>
+      <xdr:colOff>3828600</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>999720</xdr:rowOff>
+      <xdr:rowOff>999360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1388,7 +1388,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="35646840"/>
-          <a:ext cx="3828960" cy="999720"/>
+          <a:ext cx="3828600" cy="999360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1410,9 +1410,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3238560</xdr:colOff>
+      <xdr:colOff>3238200</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>1028160</xdr:rowOff>
+      <xdr:rowOff>1027800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1426,7 +1426,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="36784440"/>
-          <a:ext cx="3238560" cy="1028160"/>
+          <a:ext cx="3238200" cy="1027800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1448,9 +1448,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3209760</xdr:colOff>
+      <xdr:colOff>3209400</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>1161720</xdr:rowOff>
+      <xdr:rowOff>1161360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1464,7 +1464,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="37959120"/>
-          <a:ext cx="3209760" cy="1161720"/>
+          <a:ext cx="3209400" cy="1161360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1486,9 +1486,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3724200</xdr:colOff>
+      <xdr:colOff>3723840</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>1056960</xdr:rowOff>
+      <xdr:rowOff>1056600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1502,7 +1502,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="39399120"/>
-          <a:ext cx="3724200" cy="1056960"/>
+          <a:ext cx="3723840" cy="1056600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1524,9 +1524,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3457440</xdr:colOff>
+      <xdr:colOff>3457080</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>1009080</xdr:rowOff>
+      <xdr:rowOff>1008720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1540,7 +1540,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="40763880"/>
-          <a:ext cx="3457440" cy="1009080"/>
+          <a:ext cx="3457080" cy="1008720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1562,9 +1562,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4210200</xdr:colOff>
+      <xdr:colOff>4209840</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>1485720</xdr:rowOff>
+      <xdr:rowOff>1485360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1578,7 +1578,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="42014880"/>
-          <a:ext cx="4210200" cy="1485720"/>
+          <a:ext cx="4209840" cy="1485360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1600,9 +1600,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3390840</xdr:colOff>
+      <xdr:colOff>3390480</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>1085400</xdr:rowOff>
+      <xdr:rowOff>1085040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1616,7 +1616,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="43701480"/>
-          <a:ext cx="3390840" cy="1085400"/>
+          <a:ext cx="3390480" cy="1085040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1638,9 +1638,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3400200</xdr:colOff>
+      <xdr:colOff>3399840</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>980640</xdr:rowOff>
+      <xdr:rowOff>980280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1654,7 +1654,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="44989920"/>
-          <a:ext cx="3400200" cy="980640"/>
+          <a:ext cx="3399840" cy="980280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1676,9 +1676,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4067280</xdr:colOff>
+      <xdr:colOff>4066920</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>1056960</xdr:rowOff>
+      <xdr:rowOff>1056600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1692,7 +1692,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="46221480"/>
-          <a:ext cx="4067280" cy="1056960"/>
+          <a:ext cx="4066920" cy="1056600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1714,9 +1714,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3267000</xdr:colOff>
+      <xdr:colOff>3266640</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>1266480</xdr:rowOff>
+      <xdr:rowOff>1266120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1730,7 +1730,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="47529000"/>
-          <a:ext cx="3267000" cy="1266480"/>
+          <a:ext cx="3266640" cy="1266120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1752,9 +1752,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3476520</xdr:colOff>
+      <xdr:colOff>3476160</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>923400</xdr:rowOff>
+      <xdr:rowOff>923040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1768,7 +1768,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="49045320"/>
-          <a:ext cx="3476520" cy="923400"/>
+          <a:ext cx="3476160" cy="923040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1790,9 +1790,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4076640</xdr:colOff>
+      <xdr:colOff>4076280</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>1076040</xdr:rowOff>
+      <xdr:rowOff>1075680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1806,7 +1806,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="50125680"/>
-          <a:ext cx="4076640" cy="1076040"/>
+          <a:ext cx="4076280" cy="1075680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1828,9 +1828,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3467160</xdr:colOff>
+      <xdr:colOff>3466800</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>666360</xdr:rowOff>
+      <xdr:rowOff>666000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1844,7 +1844,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="51395040"/>
-          <a:ext cx="3467160" cy="666360"/>
+          <a:ext cx="3466800" cy="666000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1866,9 +1866,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2676240</xdr:colOff>
+      <xdr:colOff>2675880</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>914040</xdr:rowOff>
+      <xdr:rowOff>913680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1882,7 +1882,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="52171560"/>
-          <a:ext cx="2676240" cy="914040"/>
+          <a:ext cx="2675880" cy="913680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1904,9 +1904,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2485800</xdr:colOff>
+      <xdr:colOff>2485440</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>675720</xdr:rowOff>
+      <xdr:rowOff>675360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1920,7 +1920,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="53213760"/>
-          <a:ext cx="2485800" cy="675720"/>
+          <a:ext cx="2485440" cy="675360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2047,8 +2047,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="18.55" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D1048576"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="18.55" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="51.75"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
@@ -2470,7 +2470,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="37.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/src/main/resources/espacios/mathematical/0 - Mathematical Symbols.xlsx
+++ b/src/main/resources/espacios/mathematical/0 - Mathematical Symbols.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
   <si>
     <t xml:space="preserve">Plus</t>
   </si>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">ˈmaɪnəs</t>
   </si>
   <si>
+    <t xml:space="preserve">EXAMPLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Multiplied by</t>
   </si>
   <si>
@@ -334,10 +337,25 @@
     <t xml:space="preserve">Perpendicular</t>
   </si>
   <si>
+    <t xml:space="preserve">ˌpɜrpənˈdɪkjələr</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exists</t>
   </si>
   <si>
+    <t xml:space="preserve">Existe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪɡˈzɪsts</t>
+  </si>
+  <si>
     <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porcentaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pərˈsɛnt</t>
   </si>
 </sst>
 </file>
@@ -460,9 +478,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3762000</xdr:colOff>
+      <xdr:colOff>3761640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>875520</xdr:rowOff>
+      <xdr:rowOff>875160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -476,7 +494,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="0"/>
-          <a:ext cx="3762000" cy="875520"/>
+          <a:ext cx="3761640" cy="875160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -498,9 +516,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4543200</xdr:colOff>
+      <xdr:colOff>4542840</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>961200</xdr:rowOff>
+      <xdr:rowOff>960840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -514,7 +532,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="1080000"/>
-          <a:ext cx="4543200" cy="961200"/>
+          <a:ext cx="4542840" cy="960840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -536,9 +554,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4962240</xdr:colOff>
+      <xdr:colOff>4961880</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>1342440</xdr:rowOff>
+      <xdr:rowOff>1342080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -552,7 +570,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="2217600"/>
-          <a:ext cx="4962240" cy="1342440"/>
+          <a:ext cx="4961880" cy="1342080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -574,9 +592,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4819320</xdr:colOff>
+      <xdr:colOff>4818960</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>1285200</xdr:rowOff>
+      <xdr:rowOff>1284840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -590,7 +608,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="3809520"/>
-          <a:ext cx="4819320" cy="1285200"/>
+          <a:ext cx="4818960" cy="1284840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -612,9 +630,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4962240</xdr:colOff>
+      <xdr:colOff>4961880</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1713960</xdr:rowOff>
+      <xdr:rowOff>1713600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -628,7 +646,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="5325840"/>
-          <a:ext cx="4962240" cy="1713960"/>
+          <a:ext cx="4961880" cy="1713600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -650,9 +668,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4886280</xdr:colOff>
+      <xdr:colOff>4885920</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1104120</xdr:rowOff>
+      <xdr:rowOff>1103760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -666,7 +684,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="7277760"/>
-          <a:ext cx="4886280" cy="1104120"/>
+          <a:ext cx="4885920" cy="1103760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -688,9 +706,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4790880</xdr:colOff>
+      <xdr:colOff>4790520</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>1056600</xdr:rowOff>
+      <xdr:rowOff>1056240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -704,7 +722,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="8661240"/>
-          <a:ext cx="4790880" cy="1056600"/>
+          <a:ext cx="4790520" cy="1056240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -726,9 +744,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4790880</xdr:colOff>
+      <xdr:colOff>4790520</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>970920</xdr:rowOff>
+      <xdr:rowOff>970560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -742,7 +760,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="9855360"/>
-          <a:ext cx="4790880" cy="970920"/>
+          <a:ext cx="4790520" cy="970560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -764,9 +782,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5486400</xdr:colOff>
+      <xdr:colOff>5486040</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>1694880</xdr:rowOff>
+      <xdr:rowOff>1694520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -780,7 +798,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="11087280"/>
-          <a:ext cx="5486400" cy="1694880"/>
+          <a:ext cx="5486040" cy="1694520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -802,9 +820,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4962240</xdr:colOff>
+      <xdr:colOff>4961880</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>999360</xdr:rowOff>
+      <xdr:rowOff>999000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -818,7 +836,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="12925440"/>
-          <a:ext cx="4962240" cy="999360"/>
+          <a:ext cx="4961880" cy="999000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -840,9 +858,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5648040</xdr:colOff>
+      <xdr:colOff>5647680</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>1428120</xdr:rowOff>
+      <xdr:rowOff>1427760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -856,7 +874,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="14194800"/>
-          <a:ext cx="5648040" cy="1428120"/>
+          <a:ext cx="5647680" cy="1427760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -878,9 +896,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4552560</xdr:colOff>
+      <xdr:colOff>4552200</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>1170720</xdr:rowOff>
+      <xdr:rowOff>1170360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -894,7 +912,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="15786720"/>
-          <a:ext cx="4552560" cy="1170720"/>
+          <a:ext cx="4552200" cy="1170360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -916,9 +934,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5419440</xdr:colOff>
+      <xdr:colOff>5419080</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>1532880</xdr:rowOff>
+      <xdr:rowOff>1532520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -932,7 +950,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="17264880"/>
-          <a:ext cx="5419440" cy="1532880"/>
+          <a:ext cx="5419080" cy="1532520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -954,9 +972,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5391000</xdr:colOff>
+      <xdr:colOff>5390640</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>1618560</xdr:rowOff>
+      <xdr:rowOff>1618200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -970,7 +988,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="19046160"/>
-          <a:ext cx="5391000" cy="1618560"/>
+          <a:ext cx="5390640" cy="1618200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -992,9 +1010,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5715000</xdr:colOff>
+      <xdr:colOff>5714640</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>932760</xdr:rowOff>
+      <xdr:rowOff>932400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1008,7 +1026,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="20998080"/>
-          <a:ext cx="5715000" cy="932760"/>
+          <a:ext cx="5714640" cy="932400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1030,9 +1048,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4428720</xdr:colOff>
+      <xdr:colOff>4428360</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>990000</xdr:rowOff>
+      <xdr:rowOff>989640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1046,7 +1064,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="22116240"/>
-          <a:ext cx="4428720" cy="990000"/>
+          <a:ext cx="4428360" cy="989640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1068,9 +1086,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3933360</xdr:colOff>
+      <xdr:colOff>3933000</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1523160</xdr:rowOff>
+      <xdr:rowOff>1522800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1084,7 +1102,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="23385960"/>
-          <a:ext cx="3933360" cy="1523160"/>
+          <a:ext cx="3933000" cy="1522800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1106,9 +1124,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4562280</xdr:colOff>
+      <xdr:colOff>4561920</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>1380240</xdr:rowOff>
+      <xdr:rowOff>1379880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1122,7 +1140,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="25185960"/>
-          <a:ext cx="4562280" cy="1380240"/>
+          <a:ext cx="4561920" cy="1379880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1144,9 +1162,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5886360</xdr:colOff>
+      <xdr:colOff>5886000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>1551960</xdr:rowOff>
+      <xdr:rowOff>1551600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1160,7 +1178,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="26816040"/>
-          <a:ext cx="5886360" cy="1551960"/>
+          <a:ext cx="5886000" cy="1551600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1182,9 +1200,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3762000</xdr:colOff>
+      <xdr:colOff>3761640</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>1380240</xdr:rowOff>
+      <xdr:rowOff>1379880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1198,7 +1216,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="28597320"/>
-          <a:ext cx="3762000" cy="1380240"/>
+          <a:ext cx="3761640" cy="1379880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1220,9 +1238,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4447800</xdr:colOff>
+      <xdr:colOff>4447440</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1218600</xdr:rowOff>
+      <xdr:rowOff>1218240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1236,7 +1254,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="30246480"/>
-          <a:ext cx="4447800" cy="1218600"/>
+          <a:ext cx="4447440" cy="1218240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1258,9 +1276,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3390480</xdr:colOff>
+      <xdr:colOff>3390120</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>923040</xdr:rowOff>
+      <xdr:rowOff>922680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1274,7 +1292,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="31781160"/>
-          <a:ext cx="3390480" cy="923040"/>
+          <a:ext cx="3390120" cy="922680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1296,9 +1314,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3323880</xdr:colOff>
+      <xdr:colOff>3323520</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>1065960</xdr:rowOff>
+      <xdr:rowOff>1065600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1312,7 +1330,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="32936760"/>
-          <a:ext cx="3323880" cy="1065960"/>
+          <a:ext cx="3323520" cy="1065600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1334,9 +1352,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3981240</xdr:colOff>
+      <xdr:colOff>3980880</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>1142280</xdr:rowOff>
+      <xdr:rowOff>1141920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1350,7 +1368,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="34263360"/>
-          <a:ext cx="3981240" cy="1142280"/>
+          <a:ext cx="3980880" cy="1141920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1372,9 +1390,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3828600</xdr:colOff>
+      <xdr:colOff>3828240</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>999360</xdr:rowOff>
+      <xdr:rowOff>999000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1388,7 +1406,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="35646840"/>
-          <a:ext cx="3828600" cy="999360"/>
+          <a:ext cx="3828240" cy="999000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1410,9 +1428,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3238200</xdr:colOff>
+      <xdr:colOff>3237840</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>1027800</xdr:rowOff>
+      <xdr:rowOff>1027440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1426,7 +1444,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="36784440"/>
-          <a:ext cx="3238200" cy="1027800"/>
+          <a:ext cx="3237840" cy="1027440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1448,9 +1466,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3209400</xdr:colOff>
+      <xdr:colOff>3209040</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>1161360</xdr:rowOff>
+      <xdr:rowOff>1161000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1464,7 +1482,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="37959120"/>
-          <a:ext cx="3209400" cy="1161360"/>
+          <a:ext cx="3209040" cy="1161000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1486,9 +1504,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3723840</xdr:colOff>
+      <xdr:colOff>3723480</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>1056600</xdr:rowOff>
+      <xdr:rowOff>1056240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1502,7 +1520,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="39399120"/>
-          <a:ext cx="3723840" cy="1056600"/>
+          <a:ext cx="3723480" cy="1056240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1524,9 +1542,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3457080</xdr:colOff>
+      <xdr:colOff>3456720</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>1008720</xdr:rowOff>
+      <xdr:rowOff>1008360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1540,7 +1558,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="40763880"/>
-          <a:ext cx="3457080" cy="1008720"/>
+          <a:ext cx="3456720" cy="1008360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1562,9 +1580,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4209840</xdr:colOff>
+      <xdr:colOff>4209480</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>1485360</xdr:rowOff>
+      <xdr:rowOff>1485000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1578,7 +1596,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="42014880"/>
-          <a:ext cx="4209840" cy="1485360"/>
+          <a:ext cx="4209480" cy="1485000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1600,9 +1618,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3390480</xdr:colOff>
+      <xdr:colOff>3390120</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>1085040</xdr:rowOff>
+      <xdr:rowOff>1084680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1616,7 +1634,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="43701480"/>
-          <a:ext cx="3390480" cy="1085040"/>
+          <a:ext cx="3390120" cy="1084680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1638,9 +1656,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3399840</xdr:colOff>
+      <xdr:colOff>3399480</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>980280</xdr:rowOff>
+      <xdr:rowOff>979920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1654,7 +1672,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="44989920"/>
-          <a:ext cx="3399840" cy="980280"/>
+          <a:ext cx="3399480" cy="979920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1676,9 +1694,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4066920</xdr:colOff>
+      <xdr:colOff>4066560</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>1056600</xdr:rowOff>
+      <xdr:rowOff>1056240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1692,7 +1710,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="46221480"/>
-          <a:ext cx="4066920" cy="1056600"/>
+          <a:ext cx="4066560" cy="1056240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1714,9 +1732,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3266640</xdr:colOff>
+      <xdr:colOff>3266280</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>1266120</xdr:rowOff>
+      <xdr:rowOff>1265760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1730,7 +1748,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="47529000"/>
-          <a:ext cx="3266640" cy="1266120"/>
+          <a:ext cx="3266280" cy="1265760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1752,9 +1770,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3476160</xdr:colOff>
+      <xdr:colOff>3475800</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>923040</xdr:rowOff>
+      <xdr:rowOff>922680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1768,7 +1786,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="49045320"/>
-          <a:ext cx="3476160" cy="923040"/>
+          <a:ext cx="3475800" cy="922680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1790,9 +1808,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4076280</xdr:colOff>
+      <xdr:colOff>4075920</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>1075680</xdr:rowOff>
+      <xdr:rowOff>1075320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1806,7 +1824,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="50125680"/>
-          <a:ext cx="4076280" cy="1075680"/>
+          <a:ext cx="4075920" cy="1075320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1828,9 +1846,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3466800</xdr:colOff>
+      <xdr:colOff>3466440</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>666000</xdr:rowOff>
+      <xdr:rowOff>665640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1844,7 +1862,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="51395040"/>
-          <a:ext cx="3466800" cy="666000"/>
+          <a:ext cx="3466440" cy="665640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1866,9 +1884,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2675880</xdr:colOff>
+      <xdr:colOff>2675520</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>913680</xdr:rowOff>
+      <xdr:rowOff>913320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1882,7 +1900,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="52171560"/>
-          <a:ext cx="2675880" cy="913680"/>
+          <a:ext cx="2675520" cy="913320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1904,9 +1922,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2485440</xdr:colOff>
+      <xdr:colOff>2485080</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>675360</xdr:rowOff>
+      <xdr:rowOff>675000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1920,7 +1938,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11770200" y="53213760"/>
-          <a:ext cx="2485440" cy="675360"/>
+          <a:ext cx="2485080" cy="675000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2047,7 +2065,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
+  <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="18.55" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="51.75"/>
@@ -2080,394 +2098,523 @@
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="125.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="119.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="153.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="94" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="97" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="99.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="125.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="116.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="140.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="153.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="88.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="99.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="141.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="128.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="140.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="129.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="120.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="91" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="104.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="92.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="107.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="98.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="132.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="101.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="97" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="119.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="99.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="65.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
